--- a/generated/spreadsheet/listed-building-consent-lbc.xlsx
+++ b/generated/spreadsheet/listed-building-consent-lbc.xlsx
@@ -808,7 +808,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3610,7 +3610,7 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">

--- a/generated/spreadsheet/listed-building-consent-lbc.xlsx
+++ b/generated/spreadsheet/listed-building-consent-lbc.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
+          <t>Listed building grade known</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2676,12 +2676,12 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Set to true if the applicant knows the listed building grade. Set to false if they do not know it.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2703,17 +2703,17 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2730,12 +2730,12 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2745,19 +2745,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2765,43 +2757,47 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2820,24 +2816,24 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2851,14 +2847,14 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2882,19 +2878,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2908,15 +2904,19 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Materials not known</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2935,24 +2935,20 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -2962,32 +2958,28 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -2997,37 +2989,37 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3046,13 +3038,13 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3062,7 +3054,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3081,13 +3073,13 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3116,17 +3108,13 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Contact address</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Last Name</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Text representation of an address or site</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3160,12 +3148,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Postcode for a contact address or site</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3175,7 +3163,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3199,12 +3187,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>UPRN</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Number for a property</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3228,19 +3216,27 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3254,20 +3250,24 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
+          <t>Ownership certificate type</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3289,12 +3289,12 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -3308,19 +3308,15 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -3330,7 +3326,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3344,19 +3340,19 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Publication date</t>
+          <t>Newspaper name</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -3370,20 +3366,24 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -3405,12 +3405,12 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -3432,12 +3432,12 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -3447,19 +3447,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3467,12 +3459,12 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -3482,11 +3474,19 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="2" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Planning officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3494,17 +3494,17 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3548,12 +3548,12 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -3590,19 +3590,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -3610,7 +3602,7 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -3620,16 +3612,24 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3637,12 +3637,12 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
@@ -3664,17 +3664,17 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
@@ -3691,17 +3691,17 @@
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
@@ -3718,34 +3718,26 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
@@ -3753,43 +3745,47 @@
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3808,14 +3804,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3839,69 +3835,69 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>A polygon or multipolygon boundary</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>multipolygon</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="2" t="n"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3909,23 +3905,19 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Site boundary</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Text representation of an address or site</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -3949,13 +3941,13 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Postcode for a contact address or site</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -3965,7 +3957,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3984,13 +3976,13 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -4019,13 +4011,13 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>USRNs[]</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -4049,19 +4041,23 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -4080,14 +4076,14 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -4111,19 +4107,19 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -4142,19 +4138,19 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -4164,46 +4160,50 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="2" t="n"/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
@@ -4211,12 +4211,12 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
@@ -4238,17 +4238,17 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4257,19 +4257,15 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -4279,7 +4275,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4293,14 +4289,14 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -4324,22 +4320,53 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4347,46 +4374,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A71:A77"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="A37:A43"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="A47:A49"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="B115:B120"/>
+    <mergeCell ref="B107:B115"/>
+    <mergeCell ref="A103:A106"/>
     <mergeCell ref="A44"/>
     <mergeCell ref="B37:B43"/>
-    <mergeCell ref="A97:A101"/>
     <mergeCell ref="B53:B61"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B77:B91"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="A78:A92"/>
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="A64:A66"/>
     <mergeCell ref="B47:B49"/>
     <mergeCell ref="B24:B32"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A106:A114"/>
+    <mergeCell ref="A93:A97"/>
+    <mergeCell ref="B103:B106"/>
     <mergeCell ref="A53:A61"/>
-    <mergeCell ref="B97:B101"/>
-    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="B78:B92"/>
+    <mergeCell ref="B116:B121"/>
     <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A98:A102"/>
     <mergeCell ref="B33:B36"/>
     <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A116:A121"/>
     <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B93:B97"/>
     <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B106:B114"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="A70:A76"/>
+    <mergeCell ref="B71:B77"/>
     <mergeCell ref="A24:A32"/>
     <mergeCell ref="B44"/>
-    <mergeCell ref="B70:B76"/>
+    <mergeCell ref="A107:A115"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A77:A91"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A115:A120"/>
+    <mergeCell ref="B98:B102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
